--- a/src/main/resources/TermsandConditions_Field_Values.xlsx
+++ b/src/main/resources/TermsandConditions_Field_Values.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="25330"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27628"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\rei proj\product_automation\govgrants-product-automation\src\main\resources\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\New Project\ProdLWC_Mine\govgrants-product-automation\src\main\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E22D9F97-2E46-44B0-AFA8-A8BFBD1626CE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8129927A-D3D8-43F4-9880-52F14150EFF5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="20490" windowHeight="10920" xr2:uid="{1723DB62-37ED-4AF2-A84E-95702473D7B6}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{1723DB62-37ED-4AF2-A84E-95702473D7B6}"/>
   </bookViews>
   <sheets>
     <sheet name="Creation" sheetId="1" r:id="rId1"/>
@@ -50,22 +50,22 @@
     <t>Term</t>
   </si>
   <si>
-    <t>fieldAutoAddToAward__c</t>
-  </si>
-  <si>
     <t>checked</t>
   </si>
   <si>
-    <t>fieldEffectiveFrom__c</t>
-  </si>
-  <si>
-    <t>fieldEffectiveTill__c</t>
-  </si>
-  <si>
-    <t>fieldTermType__c</t>
-  </si>
-  <si>
-    <t>fieldTitle__c</t>
+    <t>Title__c</t>
+  </si>
+  <si>
+    <t>TermType__c</t>
+  </si>
+  <si>
+    <t>EffectiveFrom__c</t>
+  </si>
+  <si>
+    <t>EffectiveTill__c</t>
+  </si>
+  <si>
+    <t>AutoAddToAward__c</t>
   </si>
 </sst>
 </file>
@@ -152,9 +152,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -192,7 +192,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -298,7 +298,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -440,7 +440,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -472,7 +472,7 @@
         <v>3</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="C2" s="3" t="s">
         <v>4</v>
@@ -483,7 +483,7 @@
         <v>3</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>5</v>
@@ -494,7 +494,7 @@
         <v>3</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C4" s="2">
         <v>0</v>
@@ -505,7 +505,7 @@
         <v>3</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C5" s="2">
         <v>2200</v>
@@ -516,10 +516,10 @@
         <v>3</v>
       </c>
       <c r="B6" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="C6" t="s">
         <v>6</v>
-      </c>
-      <c r="C6" t="s">
-        <v>7</v>
       </c>
     </row>
   </sheetData>
